--- a/etf_holdings/2026-10-08_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.99%1,530,000</t>
+          <t>7.85%1,530,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>7.85%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.69%1,299,000</t>
+          <t>7.74%1,299,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.74%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5530</v>
+        <v>7165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.14%323,000</t>
+          <t>7.53%260,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.14%</t>
+          <t>7.53%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>323000</v>
+        <v>260000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6805</v>
+        <v>5575</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.08%260,000</t>
+          <t>7.28%323,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.08%</t>
+          <t>7.28%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>260000</v>
+        <v>323000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8460</v>
+        <v>2360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.19%183,000</t>
+          <t>6.34%665,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>6.34%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>183000</v>
+        <v>665000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2315</v>
+        <v>1285</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.16%665,000</t>
+          <t>5.85%1,127,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>665000</v>
+        <v>1127000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4835</v>
+        <v>8360</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.69%294,000</t>
+          <t>5.84%173,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>294000</v>
+        <v>173000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1245</v>
+        <v>17485</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.61%1,127,000</t>
+          <t>5.60%79,300</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1127000</v>
+        <v>79300</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5950</v>
+        <v>4690</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.05%212,000</t>
+          <t>5.57%294,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>5.57%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>212000</v>
+        <v>294000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>17750</v>
+        <v>6000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.57%64,300</t>
+          <t>5.14%212,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>5.14%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>64300</v>
+        <v>212000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.26%529,000</t>
+          <t>4.42%529,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.31%1000</t>
+          <t>-2%980</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.31%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.12%1,030,000</t>
+          <t>4.08%1,030,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.94%278,000</t>
+          <t>3.86%278,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2455</v>
+        <v>2370</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.35%341,000</t>
+          <t>3.27%341,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:11</t>
+          <t>2026-10-08 23:47:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>+0.68%5925</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5885</v>
+        <v>5925</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.82%120,000</t>
+          <t>2.87%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11790</v>
+        <v>1740</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.36%50,000</t>
+          <t>2.15%306,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>50000</v>
+        <v>306000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1720</v>
+        <v>10615</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.11%306,000</t>
+          <t>2.14%50,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>306000</v>
+        <v>50000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.85%179,000</t>
+          <t>1.84%179,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.32%200,000</t>
+          <t>1.38%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.89%99,139</t>
+          <t>0.90%99,139</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-9.95%5520</t>
+          <t>+1.72%5615</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.52%23,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.65%786</t>
+          <t>+1.91%801</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.65%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.46%146,000</t>
+          <t>0.47%146,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.15%3020</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3020</v>
+        <v>1075</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.24%20,000</t>
+          <t>0.22%50,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>-1.84%186.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1100</v>
+        <v>186.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.22%50,000</t>
+          <t>0.16%211,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>50000</v>
+        <v>211000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.52%190</t>
+          <t>-0.39%256.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>190</v>
+        <v>256.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.16%211,000</t>
+          <t>0.10%100,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>211000</v>
+        <v>100000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.59%257.5</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>257.5</v>
+        <v>304.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.10%100,000</t>
+          <t>0.05%42,650</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>100000</v>
+        <v>42650</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:12</t>
+          <t>2026-10-08 23:47:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>299.5</v>
+        <v>256</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.05%42,650</t>
+          <t>0.04%34,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>42650</v>
+        <v>34000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.63%250</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>250</v>
+        <v>6660</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.03%34,000</t>
+          <t>0.03%1,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>34000</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6845</v>
+        <v>557</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.03%1,000</t>
+          <t>0.02%10,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.89%556</t>
+          <t>+3.7%4345</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>556</v>
+        <v>4345</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.02%10,000</t>
+          <t>0.02%1,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.24%4190</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4190</v>
+        <v>147.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.02%28,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-0.82%727</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>148.5</v>
+        <v>727</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.02%28,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.68%733</t>
+          <t>+9.93%3320</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>733</v>
+        <v>3320</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.75%535</t>
+          <t>-2.43%522</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+7.05%250.5</t>
+          <t>-1%248</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>250.5</v>
+        <v>248</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.55%1205</t>
+          <t>-0.83%1195</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.14%1825</t>
+          <t>+4.93%1915</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+4.93%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1825</v>
+        <v>1915</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.58%1705</t>
+          <t>-1.17%1685</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1705</v>
+        <v>1685</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.91%167</t>
+          <t>-2.4%163</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.91%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.78%128.5</t>
+          <t>-0.39%128</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:13</t>
+          <t>2026-10-08 23:47:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+2.93%1230</t>
+          <t>-2.03%1205</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
